--- a/data/trans_orig/IP29A_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP29A_2023-Clase-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -97,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -110,6 +112,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -476,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -546,149 +551,109 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>8,94</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9,94</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9,38</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>8.938690023351672</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>9.944088217545358</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>9.383076032061972</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>7,3; 11,4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>8,16; 12,59</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8,08; 11,01</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>7.304442351502629</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>8.16499805238533</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>8.075035680781498</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>11.40426262779972</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>12.59424288803967</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>11.00672869803226</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>8,13</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>7,54</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7,82</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>6,69; 10,83</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6,33; 9,21</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6,84; 9,07</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>8.131485560315665</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>7.54228658179863</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>7.824377633013499</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>7,94</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>11,56</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>9,63</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>6.694560646052412</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>6.325132006924274</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>6.840691424088673</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>6,06; 10,97</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>8,56; 14,62</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>7,81; 11,87</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>10.82690792632306</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>9.209822754795885</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>9.067437814204794</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -696,149 +661,109 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>9,92</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8,91</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9,46</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>7.936658386402434</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>11.55800357135053</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>9.627692102897884</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>8,43; 11,63</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>7,46; 10,42</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8,38; 10,68</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>6.058916271964757</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>8.561508032482243</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>7.809207947004077</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>10.97452629115265</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>14.62252856342989</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>11.87004279666865</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>7,05</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>8,11</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>7,54</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>5,87; 8,21</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>6,35; 9,94</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6,57; 8,72</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>9.917996710100907</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>8.911226544029065</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>9.46451916465584</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>8,82</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>7,2</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>7,91</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>8.427596589818963</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>7.463268958506434</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>8.376689526123767</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>6,36; 12,98</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>5,4; 9,76</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>6,32; 10,31</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>11.6302957932071</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>10.42028619644484</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>10.67673912556618</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -846,47 +771,162 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>8,62</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>8,76</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>8,69</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>7.046006860345931</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>8.114779433468581</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>7.542750001872301</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>7,91; 9,44</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>7,99; 9,61</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>8,25; 9,36</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>5.872073043996253</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>6.346259748300151</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>6.566028849138439</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>8.21424796899986</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>9.939322102823406</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>8.719179310187345</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>8.824836245431431</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>7.204227228390563</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>7.906878356527839</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>6.35982568781024</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>5.403714244303249</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>6.323468967401007</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>12.9778227600613</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>9.756563681328515</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>10.31021744358601</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>8.623427274692345</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>8.755021444251902</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>8.685660939702146</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>7.905856333230487</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>7.98750710567544</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>8.247904187869372</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>9.441696924641395</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>9.607086703155176</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>9.358989624137836</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -894,14 +934,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
